--- a/ingestion/tests/fixtures/xlsx/consolidation_tiny.xlsx
+++ b/ingestion/tests/fixtures/xlsx/consolidation_tiny.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Working" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Working" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/ingestion/tests/fixtures/xlsx/consolidation_tiny.xlsx
+++ b/ingestion/tests/fixtures/xlsx/consolidation_tiny.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,12 +439,62 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>INTERVENTION DATE</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ACTUAL INTERVENTION DATE</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>TOPIC/ REMARKS</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>APPROVE/CONFIRMED TOTAL INTERVENTION</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ESTIMATED INTERVENTION</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>TOTAL ACTUAL EXPENSES FOR INTERVENTION</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ACTUAL EXPENSE AGAINST BTU</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>TOTAL ACTUAL BTC EXPENSE</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>PENDING FOR APPROVAL Request</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>PENDING FOR CONFIRMATION POST</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>STATE</t>
         </is>
       </c>
     </row>
@@ -469,11 +519,55 @@
           <t>Diabetes CME</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
         <v>31000</v>
       </c>
-      <c r="F2" t="n">
+      <c r="I2" t="n">
+        <v>62000</v>
+      </c>
+      <c r="J2" t="n">
         <v>15500</v>
+      </c>
+      <c r="K2" t="n">
+        <v>9300</v>
+      </c>
+      <c r="L2" t="n">
+        <v>6200</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Request Submitted Pending With Manager</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Report Approved</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Colombo</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Western</t>
+        </is>
       </c>
     </row>
   </sheetData>
